--- a/backend/src/OrderMgmt.WebApi/templates/templete_bbbg.xlsx
+++ b/backend/src/OrderMgmt.WebApi/templates/templete_bbbg.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM BAN HANG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\QLDonHang\backend\src\OrderMgmt.WebApi\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84674990-5DE1-4530-AB09-D0B5B7A018AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FA81455-62E7-44FD-A830-F301A9F62A0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="30 (761)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -89,9 +88,6 @@
     <t>Cộng tiền hàng</t>
   </si>
   <si>
-    <t>Thuế GTGT 8%</t>
-  </si>
-  <si>
     <t>Tổng cộng</t>
   </si>
   <si>
@@ -123,12 +119,15 @@
   </si>
   <si>
     <t>Còn lại thanh toán giao hàng</t>
+  </si>
+  <si>
+    <t>Thuế GTGT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -195,7 +194,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -257,102 +256,117 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -717,994 +731,995 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06206D16-EF32-470D-A007-AEBE77130883}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="139" width="9" style="2"/>
-    <col min="140" max="140" width="5.85546875" style="2" customWidth="1"/>
-    <col min="141" max="141" width="31.42578125" style="2" customWidth="1"/>
-    <col min="142" max="142" width="8.7109375" style="2" customWidth="1"/>
-    <col min="143" max="143" width="10.28515625" style="2" customWidth="1"/>
+    <col min="140" max="140" width="5.88671875" style="2" customWidth="1"/>
+    <col min="141" max="141" width="31.44140625" style="2" customWidth="1"/>
+    <col min="142" max="142" width="8.6640625" style="2" customWidth="1"/>
+    <col min="143" max="143" width="10.33203125" style="2" customWidth="1"/>
     <col min="144" max="144" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="146" max="147" width="9" style="2"/>
-    <col min="148" max="148" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="149" max="149" width="9" style="2"/>
-    <col min="150" max="150" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="151" max="395" width="9" style="2"/>
-    <col min="396" max="396" width="5.85546875" style="2" customWidth="1"/>
-    <col min="397" max="397" width="31.42578125" style="2" customWidth="1"/>
-    <col min="398" max="398" width="8.7109375" style="2" customWidth="1"/>
-    <col min="399" max="399" width="10.28515625" style="2" customWidth="1"/>
+    <col min="396" max="396" width="5.88671875" style="2" customWidth="1"/>
+    <col min="397" max="397" width="31.44140625" style="2" customWidth="1"/>
+    <col min="398" max="398" width="8.6640625" style="2" customWidth="1"/>
+    <col min="399" max="399" width="10.33203125" style="2" customWidth="1"/>
     <col min="400" max="400" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="401" max="401" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="401" max="401" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="402" max="403" width="9" style="2"/>
-    <col min="404" max="404" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="404" max="404" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="405" max="405" width="9" style="2"/>
-    <col min="406" max="406" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="406" max="406" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="407" max="651" width="9" style="2"/>
-    <col min="652" max="652" width="5.85546875" style="2" customWidth="1"/>
-    <col min="653" max="653" width="31.42578125" style="2" customWidth="1"/>
-    <col min="654" max="654" width="8.7109375" style="2" customWidth="1"/>
-    <col min="655" max="655" width="10.28515625" style="2" customWidth="1"/>
+    <col min="652" max="652" width="5.88671875" style="2" customWidth="1"/>
+    <col min="653" max="653" width="31.44140625" style="2" customWidth="1"/>
+    <col min="654" max="654" width="8.6640625" style="2" customWidth="1"/>
+    <col min="655" max="655" width="10.33203125" style="2" customWidth="1"/>
     <col min="656" max="656" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="657" max="657" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="657" max="657" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="658" max="659" width="9" style="2"/>
-    <col min="660" max="660" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="660" max="660" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="661" max="661" width="9" style="2"/>
-    <col min="662" max="662" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="662" max="662" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="663" max="907" width="9" style="2"/>
-    <col min="908" max="908" width="5.85546875" style="2" customWidth="1"/>
-    <col min="909" max="909" width="31.42578125" style="2" customWidth="1"/>
-    <col min="910" max="910" width="8.7109375" style="2" customWidth="1"/>
-    <col min="911" max="911" width="10.28515625" style="2" customWidth="1"/>
+    <col min="908" max="908" width="5.88671875" style="2" customWidth="1"/>
+    <col min="909" max="909" width="31.44140625" style="2" customWidth="1"/>
+    <col min="910" max="910" width="8.6640625" style="2" customWidth="1"/>
+    <col min="911" max="911" width="10.33203125" style="2" customWidth="1"/>
     <col min="912" max="912" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="913" max="913" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="913" max="913" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="914" max="915" width="9" style="2"/>
-    <col min="916" max="916" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="916" max="916" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="917" max="917" width="9" style="2"/>
-    <col min="918" max="918" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="918" max="918" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="919" max="1163" width="9" style="2"/>
-    <col min="1164" max="1164" width="5.85546875" style="2" customWidth="1"/>
-    <col min="1165" max="1165" width="31.42578125" style="2" customWidth="1"/>
-    <col min="1166" max="1166" width="8.7109375" style="2" customWidth="1"/>
-    <col min="1167" max="1167" width="10.28515625" style="2" customWidth="1"/>
+    <col min="1164" max="1164" width="5.88671875" style="2" customWidth="1"/>
+    <col min="1165" max="1165" width="31.44140625" style="2" customWidth="1"/>
+    <col min="1166" max="1166" width="8.6640625" style="2" customWidth="1"/>
+    <col min="1167" max="1167" width="10.33203125" style="2" customWidth="1"/>
     <col min="1168" max="1168" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="1169" max="1169" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1169" max="1169" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1170" max="1171" width="9" style="2"/>
-    <col min="1172" max="1172" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1172" max="1172" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1173" max="1173" width="9" style="2"/>
-    <col min="1174" max="1174" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1174" max="1174" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="1175" max="1419" width="9" style="2"/>
-    <col min="1420" max="1420" width="5.85546875" style="2" customWidth="1"/>
-    <col min="1421" max="1421" width="31.42578125" style="2" customWidth="1"/>
-    <col min="1422" max="1422" width="8.7109375" style="2" customWidth="1"/>
-    <col min="1423" max="1423" width="10.28515625" style="2" customWidth="1"/>
+    <col min="1420" max="1420" width="5.88671875" style="2" customWidth="1"/>
+    <col min="1421" max="1421" width="31.44140625" style="2" customWidth="1"/>
+    <col min="1422" max="1422" width="8.6640625" style="2" customWidth="1"/>
+    <col min="1423" max="1423" width="10.33203125" style="2" customWidth="1"/>
     <col min="1424" max="1424" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="1425" max="1425" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1425" max="1425" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1426" max="1427" width="9" style="2"/>
-    <col min="1428" max="1428" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1428" max="1428" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1429" max="1429" width="9" style="2"/>
-    <col min="1430" max="1430" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1430" max="1430" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="1431" max="1675" width="9" style="2"/>
-    <col min="1676" max="1676" width="5.85546875" style="2" customWidth="1"/>
-    <col min="1677" max="1677" width="31.42578125" style="2" customWidth="1"/>
-    <col min="1678" max="1678" width="8.7109375" style="2" customWidth="1"/>
-    <col min="1679" max="1679" width="10.28515625" style="2" customWidth="1"/>
+    <col min="1676" max="1676" width="5.88671875" style="2" customWidth="1"/>
+    <col min="1677" max="1677" width="31.44140625" style="2" customWidth="1"/>
+    <col min="1678" max="1678" width="8.6640625" style="2" customWidth="1"/>
+    <col min="1679" max="1679" width="10.33203125" style="2" customWidth="1"/>
     <col min="1680" max="1680" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="1681" max="1681" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1681" max="1681" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1682" max="1683" width="9" style="2"/>
-    <col min="1684" max="1684" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1684" max="1684" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1685" max="1685" width="9" style="2"/>
-    <col min="1686" max="1686" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1686" max="1686" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="1687" max="1931" width="9" style="2"/>
-    <col min="1932" max="1932" width="5.85546875" style="2" customWidth="1"/>
-    <col min="1933" max="1933" width="31.42578125" style="2" customWidth="1"/>
-    <col min="1934" max="1934" width="8.7109375" style="2" customWidth="1"/>
-    <col min="1935" max="1935" width="10.28515625" style="2" customWidth="1"/>
+    <col min="1932" max="1932" width="5.88671875" style="2" customWidth="1"/>
+    <col min="1933" max="1933" width="31.44140625" style="2" customWidth="1"/>
+    <col min="1934" max="1934" width="8.6640625" style="2" customWidth="1"/>
+    <col min="1935" max="1935" width="10.33203125" style="2" customWidth="1"/>
     <col min="1936" max="1936" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="1937" max="1937" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1937" max="1937" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1938" max="1939" width="9" style="2"/>
-    <col min="1940" max="1940" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1940" max="1940" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="1941" max="1941" width="9" style="2"/>
-    <col min="1942" max="1942" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1942" max="1942" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="1943" max="2187" width="9" style="2"/>
-    <col min="2188" max="2188" width="5.85546875" style="2" customWidth="1"/>
-    <col min="2189" max="2189" width="31.42578125" style="2" customWidth="1"/>
-    <col min="2190" max="2190" width="8.7109375" style="2" customWidth="1"/>
-    <col min="2191" max="2191" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2188" max="2188" width="5.88671875" style="2" customWidth="1"/>
+    <col min="2189" max="2189" width="31.44140625" style="2" customWidth="1"/>
+    <col min="2190" max="2190" width="8.6640625" style="2" customWidth="1"/>
+    <col min="2191" max="2191" width="10.33203125" style="2" customWidth="1"/>
     <col min="2192" max="2192" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="2193" max="2193" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2193" max="2193" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2194" max="2195" width="9" style="2"/>
-    <col min="2196" max="2196" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2196" max="2196" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2197" max="2197" width="9" style="2"/>
-    <col min="2198" max="2198" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2198" max="2198" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2199" max="2443" width="9" style="2"/>
-    <col min="2444" max="2444" width="5.85546875" style="2" customWidth="1"/>
-    <col min="2445" max="2445" width="31.42578125" style="2" customWidth="1"/>
-    <col min="2446" max="2446" width="8.7109375" style="2" customWidth="1"/>
-    <col min="2447" max="2447" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2444" max="2444" width="5.88671875" style="2" customWidth="1"/>
+    <col min="2445" max="2445" width="31.44140625" style="2" customWidth="1"/>
+    <col min="2446" max="2446" width="8.6640625" style="2" customWidth="1"/>
+    <col min="2447" max="2447" width="10.33203125" style="2" customWidth="1"/>
     <col min="2448" max="2448" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="2449" max="2449" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2449" max="2449" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2450" max="2451" width="9" style="2"/>
-    <col min="2452" max="2452" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2452" max="2452" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2453" max="2453" width="9" style="2"/>
-    <col min="2454" max="2454" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2454" max="2454" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2455" max="2699" width="9" style="2"/>
-    <col min="2700" max="2700" width="5.85546875" style="2" customWidth="1"/>
-    <col min="2701" max="2701" width="31.42578125" style="2" customWidth="1"/>
-    <col min="2702" max="2702" width="8.7109375" style="2" customWidth="1"/>
-    <col min="2703" max="2703" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2700" max="2700" width="5.88671875" style="2" customWidth="1"/>
+    <col min="2701" max="2701" width="31.44140625" style="2" customWidth="1"/>
+    <col min="2702" max="2702" width="8.6640625" style="2" customWidth="1"/>
+    <col min="2703" max="2703" width="10.33203125" style="2" customWidth="1"/>
     <col min="2704" max="2704" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="2705" max="2705" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2705" max="2705" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2706" max="2707" width="9" style="2"/>
-    <col min="2708" max="2708" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2708" max="2708" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2709" max="2709" width="9" style="2"/>
-    <col min="2710" max="2710" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2710" max="2710" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2711" max="2955" width="9" style="2"/>
-    <col min="2956" max="2956" width="5.85546875" style="2" customWidth="1"/>
-    <col min="2957" max="2957" width="31.42578125" style="2" customWidth="1"/>
-    <col min="2958" max="2958" width="8.7109375" style="2" customWidth="1"/>
-    <col min="2959" max="2959" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2956" max="2956" width="5.88671875" style="2" customWidth="1"/>
+    <col min="2957" max="2957" width="31.44140625" style="2" customWidth="1"/>
+    <col min="2958" max="2958" width="8.6640625" style="2" customWidth="1"/>
+    <col min="2959" max="2959" width="10.33203125" style="2" customWidth="1"/>
     <col min="2960" max="2960" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="2961" max="2961" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2961" max="2961" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2962" max="2963" width="9" style="2"/>
-    <col min="2964" max="2964" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2964" max="2964" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2965" max="2965" width="9" style="2"/>
-    <col min="2966" max="2966" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2966" max="2966" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2967" max="3211" width="9" style="2"/>
-    <col min="3212" max="3212" width="5.85546875" style="2" customWidth="1"/>
-    <col min="3213" max="3213" width="31.42578125" style="2" customWidth="1"/>
-    <col min="3214" max="3214" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3215" max="3215" width="10.28515625" style="2" customWidth="1"/>
+    <col min="3212" max="3212" width="5.88671875" style="2" customWidth="1"/>
+    <col min="3213" max="3213" width="31.44140625" style="2" customWidth="1"/>
+    <col min="3214" max="3214" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3215" max="3215" width="10.33203125" style="2" customWidth="1"/>
     <col min="3216" max="3216" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3217" max="3217" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3217" max="3217" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3218" max="3219" width="9" style="2"/>
-    <col min="3220" max="3220" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3220" max="3220" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3221" max="3221" width="9" style="2"/>
-    <col min="3222" max="3222" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3222" max="3222" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3223" max="3467" width="9" style="2"/>
-    <col min="3468" max="3468" width="5.85546875" style="2" customWidth="1"/>
-    <col min="3469" max="3469" width="31.42578125" style="2" customWidth="1"/>
-    <col min="3470" max="3470" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3471" max="3471" width="10.28515625" style="2" customWidth="1"/>
+    <col min="3468" max="3468" width="5.88671875" style="2" customWidth="1"/>
+    <col min="3469" max="3469" width="31.44140625" style="2" customWidth="1"/>
+    <col min="3470" max="3470" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3471" max="3471" width="10.33203125" style="2" customWidth="1"/>
     <col min="3472" max="3472" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3473" max="3473" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3473" max="3473" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3474" max="3475" width="9" style="2"/>
-    <col min="3476" max="3476" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3476" max="3476" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3477" max="3477" width="9" style="2"/>
-    <col min="3478" max="3478" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3478" max="3478" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3479" max="3723" width="9" style="2"/>
-    <col min="3724" max="3724" width="5.85546875" style="2" customWidth="1"/>
-    <col min="3725" max="3725" width="31.42578125" style="2" customWidth="1"/>
-    <col min="3726" max="3726" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3727" max="3727" width="10.28515625" style="2" customWidth="1"/>
+    <col min="3724" max="3724" width="5.88671875" style="2" customWidth="1"/>
+    <col min="3725" max="3725" width="31.44140625" style="2" customWidth="1"/>
+    <col min="3726" max="3726" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3727" max="3727" width="10.33203125" style="2" customWidth="1"/>
     <col min="3728" max="3728" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3729" max="3729" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3729" max="3729" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3730" max="3731" width="9" style="2"/>
-    <col min="3732" max="3732" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3732" max="3732" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3733" max="3733" width="9" style="2"/>
-    <col min="3734" max="3734" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3734" max="3734" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3735" max="3979" width="9" style="2"/>
-    <col min="3980" max="3980" width="5.85546875" style="2" customWidth="1"/>
-    <col min="3981" max="3981" width="31.42578125" style="2" customWidth="1"/>
-    <col min="3982" max="3982" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3983" max="3983" width="10.28515625" style="2" customWidth="1"/>
+    <col min="3980" max="3980" width="5.88671875" style="2" customWidth="1"/>
+    <col min="3981" max="3981" width="31.44140625" style="2" customWidth="1"/>
+    <col min="3982" max="3982" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3983" max="3983" width="10.33203125" style="2" customWidth="1"/>
     <col min="3984" max="3984" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3985" max="3985" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3985" max="3985" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3986" max="3987" width="9" style="2"/>
-    <col min="3988" max="3988" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3988" max="3988" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3989" max="3989" width="9" style="2"/>
-    <col min="3990" max="3990" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3990" max="3990" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3991" max="4235" width="9" style="2"/>
-    <col min="4236" max="4236" width="5.85546875" style="2" customWidth="1"/>
-    <col min="4237" max="4237" width="31.42578125" style="2" customWidth="1"/>
-    <col min="4238" max="4238" width="8.7109375" style="2" customWidth="1"/>
-    <col min="4239" max="4239" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4236" max="4236" width="5.88671875" style="2" customWidth="1"/>
+    <col min="4237" max="4237" width="31.44140625" style="2" customWidth="1"/>
+    <col min="4238" max="4238" width="8.6640625" style="2" customWidth="1"/>
+    <col min="4239" max="4239" width="10.33203125" style="2" customWidth="1"/>
     <col min="4240" max="4240" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="4241" max="4241" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4241" max="4241" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4242" max="4243" width="9" style="2"/>
-    <col min="4244" max="4244" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4244" max="4244" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4245" max="4245" width="9" style="2"/>
-    <col min="4246" max="4246" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4246" max="4246" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4247" max="4491" width="9" style="2"/>
-    <col min="4492" max="4492" width="5.85546875" style="2" customWidth="1"/>
-    <col min="4493" max="4493" width="31.42578125" style="2" customWidth="1"/>
-    <col min="4494" max="4494" width="8.7109375" style="2" customWidth="1"/>
-    <col min="4495" max="4495" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4492" max="4492" width="5.88671875" style="2" customWidth="1"/>
+    <col min="4493" max="4493" width="31.44140625" style="2" customWidth="1"/>
+    <col min="4494" max="4494" width="8.6640625" style="2" customWidth="1"/>
+    <col min="4495" max="4495" width="10.33203125" style="2" customWidth="1"/>
     <col min="4496" max="4496" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="4497" max="4497" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4497" max="4497" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4498" max="4499" width="9" style="2"/>
-    <col min="4500" max="4500" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4500" max="4500" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4501" max="4501" width="9" style="2"/>
-    <col min="4502" max="4502" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4502" max="4502" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4503" max="4747" width="9" style="2"/>
-    <col min="4748" max="4748" width="5.85546875" style="2" customWidth="1"/>
-    <col min="4749" max="4749" width="31.42578125" style="2" customWidth="1"/>
-    <col min="4750" max="4750" width="8.7109375" style="2" customWidth="1"/>
-    <col min="4751" max="4751" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4748" max="4748" width="5.88671875" style="2" customWidth="1"/>
+    <col min="4749" max="4749" width="31.44140625" style="2" customWidth="1"/>
+    <col min="4750" max="4750" width="8.6640625" style="2" customWidth="1"/>
+    <col min="4751" max="4751" width="10.33203125" style="2" customWidth="1"/>
     <col min="4752" max="4752" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="4753" max="4753" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4753" max="4753" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4754" max="4755" width="9" style="2"/>
-    <col min="4756" max="4756" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4756" max="4756" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4757" max="4757" width="9" style="2"/>
-    <col min="4758" max="4758" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4758" max="4758" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4759" max="5003" width="9" style="2"/>
-    <col min="5004" max="5004" width="5.85546875" style="2" customWidth="1"/>
-    <col min="5005" max="5005" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5006" max="5006" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5007" max="5007" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5004" max="5004" width="5.88671875" style="2" customWidth="1"/>
+    <col min="5005" max="5005" width="31.44140625" style="2" customWidth="1"/>
+    <col min="5006" max="5006" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5007" max="5007" width="10.33203125" style="2" customWidth="1"/>
     <col min="5008" max="5008" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5009" max="5009" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5009" max="5009" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5010" max="5011" width="9" style="2"/>
-    <col min="5012" max="5012" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5012" max="5012" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5013" max="5013" width="9" style="2"/>
-    <col min="5014" max="5014" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5014" max="5014" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5015" max="5259" width="9" style="2"/>
-    <col min="5260" max="5260" width="5.85546875" style="2" customWidth="1"/>
-    <col min="5261" max="5261" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5262" max="5262" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5263" max="5263" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5260" max="5260" width="5.88671875" style="2" customWidth="1"/>
+    <col min="5261" max="5261" width="31.44140625" style="2" customWidth="1"/>
+    <col min="5262" max="5262" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5263" max="5263" width="10.33203125" style="2" customWidth="1"/>
     <col min="5264" max="5264" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5265" max="5265" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5265" max="5265" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5266" max="5267" width="9" style="2"/>
-    <col min="5268" max="5268" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5268" max="5268" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5269" max="5269" width="9" style="2"/>
-    <col min="5270" max="5270" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5270" max="5270" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5271" max="5515" width="9" style="2"/>
-    <col min="5516" max="5516" width="5.85546875" style="2" customWidth="1"/>
-    <col min="5517" max="5517" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5518" max="5518" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5519" max="5519" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5516" max="5516" width="5.88671875" style="2" customWidth="1"/>
+    <col min="5517" max="5517" width="31.44140625" style="2" customWidth="1"/>
+    <col min="5518" max="5518" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5519" max="5519" width="10.33203125" style="2" customWidth="1"/>
     <col min="5520" max="5520" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5521" max="5521" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5521" max="5521" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5522" max="5523" width="9" style="2"/>
-    <col min="5524" max="5524" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5524" max="5524" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5525" max="5525" width="9" style="2"/>
-    <col min="5526" max="5526" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5526" max="5526" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5527" max="5771" width="9" style="2"/>
-    <col min="5772" max="5772" width="5.85546875" style="2" customWidth="1"/>
-    <col min="5773" max="5773" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5774" max="5774" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5775" max="5775" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5772" max="5772" width="5.88671875" style="2" customWidth="1"/>
+    <col min="5773" max="5773" width="31.44140625" style="2" customWidth="1"/>
+    <col min="5774" max="5774" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5775" max="5775" width="10.33203125" style="2" customWidth="1"/>
     <col min="5776" max="5776" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5777" max="5777" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5777" max="5777" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5778" max="5779" width="9" style="2"/>
-    <col min="5780" max="5780" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5780" max="5780" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5781" max="5781" width="9" style="2"/>
-    <col min="5782" max="5782" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5782" max="5782" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5783" max="6027" width="9" style="2"/>
-    <col min="6028" max="6028" width="5.85546875" style="2" customWidth="1"/>
-    <col min="6029" max="6029" width="31.42578125" style="2" customWidth="1"/>
-    <col min="6030" max="6030" width="8.7109375" style="2" customWidth="1"/>
-    <col min="6031" max="6031" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6028" max="6028" width="5.88671875" style="2" customWidth="1"/>
+    <col min="6029" max="6029" width="31.44140625" style="2" customWidth="1"/>
+    <col min="6030" max="6030" width="8.6640625" style="2" customWidth="1"/>
+    <col min="6031" max="6031" width="10.33203125" style="2" customWidth="1"/>
     <col min="6032" max="6032" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6033" max="6033" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6033" max="6033" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6034" max="6035" width="9" style="2"/>
-    <col min="6036" max="6036" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6036" max="6036" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6037" max="6037" width="9" style="2"/>
-    <col min="6038" max="6038" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6038" max="6038" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6039" max="6283" width="9" style="2"/>
-    <col min="6284" max="6284" width="5.85546875" style="2" customWidth="1"/>
-    <col min="6285" max="6285" width="31.42578125" style="2" customWidth="1"/>
-    <col min="6286" max="6286" width="8.7109375" style="2" customWidth="1"/>
-    <col min="6287" max="6287" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6284" max="6284" width="5.88671875" style="2" customWidth="1"/>
+    <col min="6285" max="6285" width="31.44140625" style="2" customWidth="1"/>
+    <col min="6286" max="6286" width="8.6640625" style="2" customWidth="1"/>
+    <col min="6287" max="6287" width="10.33203125" style="2" customWidth="1"/>
     <col min="6288" max="6288" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6289" max="6289" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6289" max="6289" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6290" max="6291" width="9" style="2"/>
-    <col min="6292" max="6292" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6292" max="6292" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6293" max="6293" width="9" style="2"/>
-    <col min="6294" max="6294" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6294" max="6294" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6295" max="6539" width="9" style="2"/>
-    <col min="6540" max="6540" width="5.85546875" style="2" customWidth="1"/>
-    <col min="6541" max="6541" width="31.42578125" style="2" customWidth="1"/>
-    <col min="6542" max="6542" width="8.7109375" style="2" customWidth="1"/>
-    <col min="6543" max="6543" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6540" max="6540" width="5.88671875" style="2" customWidth="1"/>
+    <col min="6541" max="6541" width="31.44140625" style="2" customWidth="1"/>
+    <col min="6542" max="6542" width="8.6640625" style="2" customWidth="1"/>
+    <col min="6543" max="6543" width="10.33203125" style="2" customWidth="1"/>
     <col min="6544" max="6544" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6545" max="6545" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6545" max="6545" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6546" max="6547" width="9" style="2"/>
-    <col min="6548" max="6548" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6548" max="6548" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6549" max="6549" width="9" style="2"/>
-    <col min="6550" max="6550" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6550" max="6550" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6551" max="6795" width="9" style="2"/>
-    <col min="6796" max="6796" width="5.85546875" style="2" customWidth="1"/>
-    <col min="6797" max="6797" width="31.42578125" style="2" customWidth="1"/>
-    <col min="6798" max="6798" width="8.7109375" style="2" customWidth="1"/>
-    <col min="6799" max="6799" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6796" max="6796" width="5.88671875" style="2" customWidth="1"/>
+    <col min="6797" max="6797" width="31.44140625" style="2" customWidth="1"/>
+    <col min="6798" max="6798" width="8.6640625" style="2" customWidth="1"/>
+    <col min="6799" max="6799" width="10.33203125" style="2" customWidth="1"/>
     <col min="6800" max="6800" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6801" max="6801" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6801" max="6801" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6802" max="6803" width="9" style="2"/>
-    <col min="6804" max="6804" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6804" max="6804" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6805" max="6805" width="9" style="2"/>
-    <col min="6806" max="6806" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6806" max="6806" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6807" max="7051" width="9" style="2"/>
-    <col min="7052" max="7052" width="5.85546875" style="2" customWidth="1"/>
-    <col min="7053" max="7053" width="31.42578125" style="2" customWidth="1"/>
-    <col min="7054" max="7054" width="8.7109375" style="2" customWidth="1"/>
-    <col min="7055" max="7055" width="10.28515625" style="2" customWidth="1"/>
+    <col min="7052" max="7052" width="5.88671875" style="2" customWidth="1"/>
+    <col min="7053" max="7053" width="31.44140625" style="2" customWidth="1"/>
+    <col min="7054" max="7054" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7055" max="7055" width="10.33203125" style="2" customWidth="1"/>
     <col min="7056" max="7056" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="7057" max="7057" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7057" max="7057" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7058" max="7059" width="9" style="2"/>
-    <col min="7060" max="7060" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7060" max="7060" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7061" max="7061" width="9" style="2"/>
-    <col min="7062" max="7062" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7062" max="7062" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7063" max="7307" width="9" style="2"/>
-    <col min="7308" max="7308" width="5.85546875" style="2" customWidth="1"/>
-    <col min="7309" max="7309" width="31.42578125" style="2" customWidth="1"/>
-    <col min="7310" max="7310" width="8.7109375" style="2" customWidth="1"/>
-    <col min="7311" max="7311" width="10.28515625" style="2" customWidth="1"/>
+    <col min="7308" max="7308" width="5.88671875" style="2" customWidth="1"/>
+    <col min="7309" max="7309" width="31.44140625" style="2" customWidth="1"/>
+    <col min="7310" max="7310" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7311" max="7311" width="10.33203125" style="2" customWidth="1"/>
     <col min="7312" max="7312" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="7313" max="7313" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7313" max="7313" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7314" max="7315" width="9" style="2"/>
-    <col min="7316" max="7316" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7316" max="7316" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7317" max="7317" width="9" style="2"/>
-    <col min="7318" max="7318" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7318" max="7318" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7319" max="7563" width="9" style="2"/>
-    <col min="7564" max="7564" width="5.85546875" style="2" customWidth="1"/>
-    <col min="7565" max="7565" width="31.42578125" style="2" customWidth="1"/>
-    <col min="7566" max="7566" width="8.7109375" style="2" customWidth="1"/>
-    <col min="7567" max="7567" width="10.28515625" style="2" customWidth="1"/>
+    <col min="7564" max="7564" width="5.88671875" style="2" customWidth="1"/>
+    <col min="7565" max="7565" width="31.44140625" style="2" customWidth="1"/>
+    <col min="7566" max="7566" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7567" max="7567" width="10.33203125" style="2" customWidth="1"/>
     <col min="7568" max="7568" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="7569" max="7569" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7569" max="7569" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7570" max="7571" width="9" style="2"/>
-    <col min="7572" max="7572" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7572" max="7572" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7573" max="7573" width="9" style="2"/>
-    <col min="7574" max="7574" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7574" max="7574" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7575" max="7819" width="9" style="2"/>
-    <col min="7820" max="7820" width="5.85546875" style="2" customWidth="1"/>
-    <col min="7821" max="7821" width="31.42578125" style="2" customWidth="1"/>
-    <col min="7822" max="7822" width="8.7109375" style="2" customWidth="1"/>
-    <col min="7823" max="7823" width="10.28515625" style="2" customWidth="1"/>
+    <col min="7820" max="7820" width="5.88671875" style="2" customWidth="1"/>
+    <col min="7821" max="7821" width="31.44140625" style="2" customWidth="1"/>
+    <col min="7822" max="7822" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7823" max="7823" width="10.33203125" style="2" customWidth="1"/>
     <col min="7824" max="7824" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="7825" max="7825" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7825" max="7825" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7826" max="7827" width="9" style="2"/>
-    <col min="7828" max="7828" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7828" max="7828" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7829" max="7829" width="9" style="2"/>
-    <col min="7830" max="7830" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7830" max="7830" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7831" max="8075" width="9" style="2"/>
-    <col min="8076" max="8076" width="5.85546875" style="2" customWidth="1"/>
-    <col min="8077" max="8077" width="31.42578125" style="2" customWidth="1"/>
-    <col min="8078" max="8078" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8079" max="8079" width="10.28515625" style="2" customWidth="1"/>
+    <col min="8076" max="8076" width="5.88671875" style="2" customWidth="1"/>
+    <col min="8077" max="8077" width="31.44140625" style="2" customWidth="1"/>
+    <col min="8078" max="8078" width="8.6640625" style="2" customWidth="1"/>
+    <col min="8079" max="8079" width="10.33203125" style="2" customWidth="1"/>
     <col min="8080" max="8080" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8081" max="8081" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8081" max="8081" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8082" max="8083" width="9" style="2"/>
-    <col min="8084" max="8084" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8084" max="8084" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8085" max="8085" width="9" style="2"/>
-    <col min="8086" max="8086" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8086" max="8086" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8087" max="8331" width="9" style="2"/>
-    <col min="8332" max="8332" width="5.85546875" style="2" customWidth="1"/>
-    <col min="8333" max="8333" width="31.42578125" style="2" customWidth="1"/>
-    <col min="8334" max="8334" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8335" max="8335" width="10.28515625" style="2" customWidth="1"/>
+    <col min="8332" max="8332" width="5.88671875" style="2" customWidth="1"/>
+    <col min="8333" max="8333" width="31.44140625" style="2" customWidth="1"/>
+    <col min="8334" max="8334" width="8.6640625" style="2" customWidth="1"/>
+    <col min="8335" max="8335" width="10.33203125" style="2" customWidth="1"/>
     <col min="8336" max="8336" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8337" max="8337" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8337" max="8337" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8338" max="8339" width="9" style="2"/>
-    <col min="8340" max="8340" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8340" max="8340" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8341" max="8341" width="9" style="2"/>
-    <col min="8342" max="8342" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8342" max="8342" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8343" max="8587" width="9" style="2"/>
-    <col min="8588" max="8588" width="5.85546875" style="2" customWidth="1"/>
-    <col min="8589" max="8589" width="31.42578125" style="2" customWidth="1"/>
-    <col min="8590" max="8590" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8591" max="8591" width="10.28515625" style="2" customWidth="1"/>
+    <col min="8588" max="8588" width="5.88671875" style="2" customWidth="1"/>
+    <col min="8589" max="8589" width="31.44140625" style="2" customWidth="1"/>
+    <col min="8590" max="8590" width="8.6640625" style="2" customWidth="1"/>
+    <col min="8591" max="8591" width="10.33203125" style="2" customWidth="1"/>
     <col min="8592" max="8592" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8593" max="8593" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8593" max="8593" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8594" max="8595" width="9" style="2"/>
-    <col min="8596" max="8596" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8596" max="8596" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8597" max="8597" width="9" style="2"/>
-    <col min="8598" max="8598" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8598" max="8598" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8599" max="8843" width="9" style="2"/>
-    <col min="8844" max="8844" width="5.85546875" style="2" customWidth="1"/>
-    <col min="8845" max="8845" width="31.42578125" style="2" customWidth="1"/>
-    <col min="8846" max="8846" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8847" max="8847" width="10.28515625" style="2" customWidth="1"/>
+    <col min="8844" max="8844" width="5.88671875" style="2" customWidth="1"/>
+    <col min="8845" max="8845" width="31.44140625" style="2" customWidth="1"/>
+    <col min="8846" max="8846" width="8.6640625" style="2" customWidth="1"/>
+    <col min="8847" max="8847" width="10.33203125" style="2" customWidth="1"/>
     <col min="8848" max="8848" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8849" max="8849" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8849" max="8849" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8850" max="8851" width="9" style="2"/>
-    <col min="8852" max="8852" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8852" max="8852" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8853" max="8853" width="9" style="2"/>
-    <col min="8854" max="8854" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8854" max="8854" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8855" max="9099" width="9" style="2"/>
-    <col min="9100" max="9100" width="5.85546875" style="2" customWidth="1"/>
-    <col min="9101" max="9101" width="31.42578125" style="2" customWidth="1"/>
-    <col min="9102" max="9102" width="8.7109375" style="2" customWidth="1"/>
-    <col min="9103" max="9103" width="10.28515625" style="2" customWidth="1"/>
+    <col min="9100" max="9100" width="5.88671875" style="2" customWidth="1"/>
+    <col min="9101" max="9101" width="31.44140625" style="2" customWidth="1"/>
+    <col min="9102" max="9102" width="8.6640625" style="2" customWidth="1"/>
+    <col min="9103" max="9103" width="10.33203125" style="2" customWidth="1"/>
     <col min="9104" max="9104" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="9105" max="9105" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9105" max="9105" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9106" max="9107" width="9" style="2"/>
-    <col min="9108" max="9108" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9108" max="9108" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9109" max="9109" width="9" style="2"/>
-    <col min="9110" max="9110" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9110" max="9110" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9111" max="9355" width="9" style="2"/>
-    <col min="9356" max="9356" width="5.85546875" style="2" customWidth="1"/>
-    <col min="9357" max="9357" width="31.42578125" style="2" customWidth="1"/>
-    <col min="9358" max="9358" width="8.7109375" style="2" customWidth="1"/>
-    <col min="9359" max="9359" width="10.28515625" style="2" customWidth="1"/>
+    <col min="9356" max="9356" width="5.88671875" style="2" customWidth="1"/>
+    <col min="9357" max="9357" width="31.44140625" style="2" customWidth="1"/>
+    <col min="9358" max="9358" width="8.6640625" style="2" customWidth="1"/>
+    <col min="9359" max="9359" width="10.33203125" style="2" customWidth="1"/>
     <col min="9360" max="9360" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="9361" max="9361" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9361" max="9361" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9362" max="9363" width="9" style="2"/>
-    <col min="9364" max="9364" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9364" max="9364" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9365" max="9365" width="9" style="2"/>
-    <col min="9366" max="9366" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9366" max="9366" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9367" max="9611" width="9" style="2"/>
-    <col min="9612" max="9612" width="5.85546875" style="2" customWidth="1"/>
-    <col min="9613" max="9613" width="31.42578125" style="2" customWidth="1"/>
-    <col min="9614" max="9614" width="8.7109375" style="2" customWidth="1"/>
-    <col min="9615" max="9615" width="10.28515625" style="2" customWidth="1"/>
+    <col min="9612" max="9612" width="5.88671875" style="2" customWidth="1"/>
+    <col min="9613" max="9613" width="31.44140625" style="2" customWidth="1"/>
+    <col min="9614" max="9614" width="8.6640625" style="2" customWidth="1"/>
+    <col min="9615" max="9615" width="10.33203125" style="2" customWidth="1"/>
     <col min="9616" max="9616" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="9617" max="9617" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9617" max="9617" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9618" max="9619" width="9" style="2"/>
-    <col min="9620" max="9620" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9620" max="9620" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9621" max="9621" width="9" style="2"/>
-    <col min="9622" max="9622" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9622" max="9622" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9623" max="9867" width="9" style="2"/>
-    <col min="9868" max="9868" width="5.85546875" style="2" customWidth="1"/>
-    <col min="9869" max="9869" width="31.42578125" style="2" customWidth="1"/>
-    <col min="9870" max="9870" width="8.7109375" style="2" customWidth="1"/>
-    <col min="9871" max="9871" width="10.28515625" style="2" customWidth="1"/>
+    <col min="9868" max="9868" width="5.88671875" style="2" customWidth="1"/>
+    <col min="9869" max="9869" width="31.44140625" style="2" customWidth="1"/>
+    <col min="9870" max="9870" width="8.6640625" style="2" customWidth="1"/>
+    <col min="9871" max="9871" width="10.33203125" style="2" customWidth="1"/>
     <col min="9872" max="9872" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="9873" max="9873" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9873" max="9873" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9874" max="9875" width="9" style="2"/>
-    <col min="9876" max="9876" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9876" max="9876" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9877" max="9877" width="9" style="2"/>
-    <col min="9878" max="9878" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9878" max="9878" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9879" max="10123" width="9" style="2"/>
-    <col min="10124" max="10124" width="5.85546875" style="2" customWidth="1"/>
-    <col min="10125" max="10125" width="31.42578125" style="2" customWidth="1"/>
-    <col min="10126" max="10126" width="8.7109375" style="2" customWidth="1"/>
-    <col min="10127" max="10127" width="10.28515625" style="2" customWidth="1"/>
+    <col min="10124" max="10124" width="5.88671875" style="2" customWidth="1"/>
+    <col min="10125" max="10125" width="31.44140625" style="2" customWidth="1"/>
+    <col min="10126" max="10126" width="8.6640625" style="2" customWidth="1"/>
+    <col min="10127" max="10127" width="10.33203125" style="2" customWidth="1"/>
     <col min="10128" max="10128" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="10129" max="10129" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10129" max="10129" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10130" max="10131" width="9" style="2"/>
-    <col min="10132" max="10132" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10132" max="10132" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10133" max="10133" width="9" style="2"/>
-    <col min="10134" max="10134" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10134" max="10134" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10135" max="10379" width="9" style="2"/>
-    <col min="10380" max="10380" width="5.85546875" style="2" customWidth="1"/>
-    <col min="10381" max="10381" width="31.42578125" style="2" customWidth="1"/>
-    <col min="10382" max="10382" width="8.7109375" style="2" customWidth="1"/>
-    <col min="10383" max="10383" width="10.28515625" style="2" customWidth="1"/>
+    <col min="10380" max="10380" width="5.88671875" style="2" customWidth="1"/>
+    <col min="10381" max="10381" width="31.44140625" style="2" customWidth="1"/>
+    <col min="10382" max="10382" width="8.6640625" style="2" customWidth="1"/>
+    <col min="10383" max="10383" width="10.33203125" style="2" customWidth="1"/>
     <col min="10384" max="10384" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="10385" max="10385" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10385" max="10385" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10386" max="10387" width="9" style="2"/>
-    <col min="10388" max="10388" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10388" max="10388" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10389" max="10389" width="9" style="2"/>
-    <col min="10390" max="10390" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10390" max="10390" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10391" max="10635" width="9" style="2"/>
-    <col min="10636" max="10636" width="5.85546875" style="2" customWidth="1"/>
-    <col min="10637" max="10637" width="31.42578125" style="2" customWidth="1"/>
-    <col min="10638" max="10638" width="8.7109375" style="2" customWidth="1"/>
-    <col min="10639" max="10639" width="10.28515625" style="2" customWidth="1"/>
+    <col min="10636" max="10636" width="5.88671875" style="2" customWidth="1"/>
+    <col min="10637" max="10637" width="31.44140625" style="2" customWidth="1"/>
+    <col min="10638" max="10638" width="8.6640625" style="2" customWidth="1"/>
+    <col min="10639" max="10639" width="10.33203125" style="2" customWidth="1"/>
     <col min="10640" max="10640" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="10641" max="10641" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10641" max="10641" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10642" max="10643" width="9" style="2"/>
-    <col min="10644" max="10644" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10644" max="10644" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10645" max="10645" width="9" style="2"/>
-    <col min="10646" max="10646" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10646" max="10646" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10647" max="10891" width="9" style="2"/>
-    <col min="10892" max="10892" width="5.85546875" style="2" customWidth="1"/>
-    <col min="10893" max="10893" width="31.42578125" style="2" customWidth="1"/>
-    <col min="10894" max="10894" width="8.7109375" style="2" customWidth="1"/>
-    <col min="10895" max="10895" width="10.28515625" style="2" customWidth="1"/>
+    <col min="10892" max="10892" width="5.88671875" style="2" customWidth="1"/>
+    <col min="10893" max="10893" width="31.44140625" style="2" customWidth="1"/>
+    <col min="10894" max="10894" width="8.6640625" style="2" customWidth="1"/>
+    <col min="10895" max="10895" width="10.33203125" style="2" customWidth="1"/>
     <col min="10896" max="10896" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="10897" max="10897" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10897" max="10897" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10898" max="10899" width="9" style="2"/>
-    <col min="10900" max="10900" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10900" max="10900" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10901" max="10901" width="9" style="2"/>
-    <col min="10902" max="10902" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10902" max="10902" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10903" max="11147" width="9" style="2"/>
-    <col min="11148" max="11148" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11149" max="11149" width="31.42578125" style="2" customWidth="1"/>
-    <col min="11150" max="11150" width="8.7109375" style="2" customWidth="1"/>
-    <col min="11151" max="11151" width="10.28515625" style="2" customWidth="1"/>
+    <col min="11148" max="11148" width="5.88671875" style="2" customWidth="1"/>
+    <col min="11149" max="11149" width="31.44140625" style="2" customWidth="1"/>
+    <col min="11150" max="11150" width="8.6640625" style="2" customWidth="1"/>
+    <col min="11151" max="11151" width="10.33203125" style="2" customWidth="1"/>
     <col min="11152" max="11152" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11153" max="11153" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11153" max="11153" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11154" max="11155" width="9" style="2"/>
-    <col min="11156" max="11156" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11156" max="11156" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11157" max="11157" width="9" style="2"/>
-    <col min="11158" max="11158" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11158" max="11158" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11159" max="11403" width="9" style="2"/>
-    <col min="11404" max="11404" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11405" max="11405" width="31.42578125" style="2" customWidth="1"/>
-    <col min="11406" max="11406" width="8.7109375" style="2" customWidth="1"/>
-    <col min="11407" max="11407" width="10.28515625" style="2" customWidth="1"/>
+    <col min="11404" max="11404" width="5.88671875" style="2" customWidth="1"/>
+    <col min="11405" max="11405" width="31.44140625" style="2" customWidth="1"/>
+    <col min="11406" max="11406" width="8.6640625" style="2" customWidth="1"/>
+    <col min="11407" max="11407" width="10.33203125" style="2" customWidth="1"/>
     <col min="11408" max="11408" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11409" max="11409" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11409" max="11409" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11410" max="11411" width="9" style="2"/>
-    <col min="11412" max="11412" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11412" max="11412" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11413" max="11413" width="9" style="2"/>
-    <col min="11414" max="11414" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11414" max="11414" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11415" max="11659" width="9" style="2"/>
-    <col min="11660" max="11660" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11661" max="11661" width="31.42578125" style="2" customWidth="1"/>
-    <col min="11662" max="11662" width="8.7109375" style="2" customWidth="1"/>
-    <col min="11663" max="11663" width="10.28515625" style="2" customWidth="1"/>
+    <col min="11660" max="11660" width="5.88671875" style="2" customWidth="1"/>
+    <col min="11661" max="11661" width="31.44140625" style="2" customWidth="1"/>
+    <col min="11662" max="11662" width="8.6640625" style="2" customWidth="1"/>
+    <col min="11663" max="11663" width="10.33203125" style="2" customWidth="1"/>
     <col min="11664" max="11664" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11665" max="11665" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11665" max="11665" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11666" max="11667" width="9" style="2"/>
-    <col min="11668" max="11668" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11668" max="11668" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11669" max="11669" width="9" style="2"/>
-    <col min="11670" max="11670" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11670" max="11670" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11671" max="11915" width="9" style="2"/>
-    <col min="11916" max="11916" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11917" max="11917" width="31.42578125" style="2" customWidth="1"/>
-    <col min="11918" max="11918" width="8.7109375" style="2" customWidth="1"/>
-    <col min="11919" max="11919" width="10.28515625" style="2" customWidth="1"/>
+    <col min="11916" max="11916" width="5.88671875" style="2" customWidth="1"/>
+    <col min="11917" max="11917" width="31.44140625" style="2" customWidth="1"/>
+    <col min="11918" max="11918" width="8.6640625" style="2" customWidth="1"/>
+    <col min="11919" max="11919" width="10.33203125" style="2" customWidth="1"/>
     <col min="11920" max="11920" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11921" max="11921" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11921" max="11921" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11922" max="11923" width="9" style="2"/>
-    <col min="11924" max="11924" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11924" max="11924" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11925" max="11925" width="9" style="2"/>
-    <col min="11926" max="11926" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11926" max="11926" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11927" max="12171" width="9" style="2"/>
-    <col min="12172" max="12172" width="5.85546875" style="2" customWidth="1"/>
-    <col min="12173" max="12173" width="31.42578125" style="2" customWidth="1"/>
-    <col min="12174" max="12174" width="8.7109375" style="2" customWidth="1"/>
-    <col min="12175" max="12175" width="10.28515625" style="2" customWidth="1"/>
+    <col min="12172" max="12172" width="5.88671875" style="2" customWidth="1"/>
+    <col min="12173" max="12173" width="31.44140625" style="2" customWidth="1"/>
+    <col min="12174" max="12174" width="8.6640625" style="2" customWidth="1"/>
+    <col min="12175" max="12175" width="10.33203125" style="2" customWidth="1"/>
     <col min="12176" max="12176" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="12177" max="12177" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12177" max="12177" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12178" max="12179" width="9" style="2"/>
-    <col min="12180" max="12180" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12180" max="12180" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12181" max="12181" width="9" style="2"/>
-    <col min="12182" max="12182" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12182" max="12182" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12183" max="12427" width="9" style="2"/>
-    <col min="12428" max="12428" width="5.85546875" style="2" customWidth="1"/>
-    <col min="12429" max="12429" width="31.42578125" style="2" customWidth="1"/>
-    <col min="12430" max="12430" width="8.7109375" style="2" customWidth="1"/>
-    <col min="12431" max="12431" width="10.28515625" style="2" customWidth="1"/>
+    <col min="12428" max="12428" width="5.88671875" style="2" customWidth="1"/>
+    <col min="12429" max="12429" width="31.44140625" style="2" customWidth="1"/>
+    <col min="12430" max="12430" width="8.6640625" style="2" customWidth="1"/>
+    <col min="12431" max="12431" width="10.33203125" style="2" customWidth="1"/>
     <col min="12432" max="12432" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="12433" max="12433" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12433" max="12433" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12434" max="12435" width="9" style="2"/>
-    <col min="12436" max="12436" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12436" max="12436" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12437" max="12437" width="9" style="2"/>
-    <col min="12438" max="12438" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12438" max="12438" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12439" max="12683" width="9" style="2"/>
-    <col min="12684" max="12684" width="5.85546875" style="2" customWidth="1"/>
-    <col min="12685" max="12685" width="31.42578125" style="2" customWidth="1"/>
-    <col min="12686" max="12686" width="8.7109375" style="2" customWidth="1"/>
-    <col min="12687" max="12687" width="10.28515625" style="2" customWidth="1"/>
+    <col min="12684" max="12684" width="5.88671875" style="2" customWidth="1"/>
+    <col min="12685" max="12685" width="31.44140625" style="2" customWidth="1"/>
+    <col min="12686" max="12686" width="8.6640625" style="2" customWidth="1"/>
+    <col min="12687" max="12687" width="10.33203125" style="2" customWidth="1"/>
     <col min="12688" max="12688" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="12689" max="12689" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12689" max="12689" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12690" max="12691" width="9" style="2"/>
-    <col min="12692" max="12692" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12692" max="12692" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12693" max="12693" width="9" style="2"/>
-    <col min="12694" max="12694" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12694" max="12694" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12695" max="12939" width="9" style="2"/>
-    <col min="12940" max="12940" width="5.85546875" style="2" customWidth="1"/>
-    <col min="12941" max="12941" width="31.42578125" style="2" customWidth="1"/>
-    <col min="12942" max="12942" width="8.7109375" style="2" customWidth="1"/>
-    <col min="12943" max="12943" width="10.28515625" style="2" customWidth="1"/>
+    <col min="12940" max="12940" width="5.88671875" style="2" customWidth="1"/>
+    <col min="12941" max="12941" width="31.44140625" style="2" customWidth="1"/>
+    <col min="12942" max="12942" width="8.6640625" style="2" customWidth="1"/>
+    <col min="12943" max="12943" width="10.33203125" style="2" customWidth="1"/>
     <col min="12944" max="12944" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="12945" max="12945" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12945" max="12945" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12946" max="12947" width="9" style="2"/>
-    <col min="12948" max="12948" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12948" max="12948" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12949" max="12949" width="9" style="2"/>
-    <col min="12950" max="12950" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12950" max="12950" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12951" max="13195" width="9" style="2"/>
-    <col min="13196" max="13196" width="5.85546875" style="2" customWidth="1"/>
-    <col min="13197" max="13197" width="31.42578125" style="2" customWidth="1"/>
-    <col min="13198" max="13198" width="8.7109375" style="2" customWidth="1"/>
-    <col min="13199" max="13199" width="10.28515625" style="2" customWidth="1"/>
+    <col min="13196" max="13196" width="5.88671875" style="2" customWidth="1"/>
+    <col min="13197" max="13197" width="31.44140625" style="2" customWidth="1"/>
+    <col min="13198" max="13198" width="8.6640625" style="2" customWidth="1"/>
+    <col min="13199" max="13199" width="10.33203125" style="2" customWidth="1"/>
     <col min="13200" max="13200" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13201" max="13201" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13201" max="13201" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13202" max="13203" width="9" style="2"/>
-    <col min="13204" max="13204" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13204" max="13204" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13205" max="13205" width="9" style="2"/>
-    <col min="13206" max="13206" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13206" max="13206" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13207" max="13451" width="9" style="2"/>
-    <col min="13452" max="13452" width="5.85546875" style="2" customWidth="1"/>
-    <col min="13453" max="13453" width="31.42578125" style="2" customWidth="1"/>
-    <col min="13454" max="13454" width="8.7109375" style="2" customWidth="1"/>
-    <col min="13455" max="13455" width="10.28515625" style="2" customWidth="1"/>
+    <col min="13452" max="13452" width="5.88671875" style="2" customWidth="1"/>
+    <col min="13453" max="13453" width="31.44140625" style="2" customWidth="1"/>
+    <col min="13454" max="13454" width="8.6640625" style="2" customWidth="1"/>
+    <col min="13455" max="13455" width="10.33203125" style="2" customWidth="1"/>
     <col min="13456" max="13456" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13457" max="13457" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13457" max="13457" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13458" max="13459" width="9" style="2"/>
-    <col min="13460" max="13460" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13460" max="13460" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13461" max="13461" width="9" style="2"/>
-    <col min="13462" max="13462" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13462" max="13462" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13463" max="13707" width="9" style="2"/>
-    <col min="13708" max="13708" width="5.85546875" style="2" customWidth="1"/>
-    <col min="13709" max="13709" width="31.42578125" style="2" customWidth="1"/>
-    <col min="13710" max="13710" width="8.7109375" style="2" customWidth="1"/>
-    <col min="13711" max="13711" width="10.28515625" style="2" customWidth="1"/>
+    <col min="13708" max="13708" width="5.88671875" style="2" customWidth="1"/>
+    <col min="13709" max="13709" width="31.44140625" style="2" customWidth="1"/>
+    <col min="13710" max="13710" width="8.6640625" style="2" customWidth="1"/>
+    <col min="13711" max="13711" width="10.33203125" style="2" customWidth="1"/>
     <col min="13712" max="13712" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13713" max="13713" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13713" max="13713" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13714" max="13715" width="9" style="2"/>
-    <col min="13716" max="13716" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13716" max="13716" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13717" max="13717" width="9" style="2"/>
-    <col min="13718" max="13718" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13718" max="13718" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13719" max="13963" width="9" style="2"/>
-    <col min="13964" max="13964" width="5.85546875" style="2" customWidth="1"/>
-    <col min="13965" max="13965" width="31.42578125" style="2" customWidth="1"/>
-    <col min="13966" max="13966" width="8.7109375" style="2" customWidth="1"/>
-    <col min="13967" max="13967" width="10.28515625" style="2" customWidth="1"/>
+    <col min="13964" max="13964" width="5.88671875" style="2" customWidth="1"/>
+    <col min="13965" max="13965" width="31.44140625" style="2" customWidth="1"/>
+    <col min="13966" max="13966" width="8.6640625" style="2" customWidth="1"/>
+    <col min="13967" max="13967" width="10.33203125" style="2" customWidth="1"/>
     <col min="13968" max="13968" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13969" max="13969" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13969" max="13969" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13970" max="13971" width="9" style="2"/>
-    <col min="13972" max="13972" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13972" max="13972" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13973" max="13973" width="9" style="2"/>
-    <col min="13974" max="13974" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13974" max="13974" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13975" max="14219" width="9" style="2"/>
-    <col min="14220" max="14220" width="5.85546875" style="2" customWidth="1"/>
-    <col min="14221" max="14221" width="31.42578125" style="2" customWidth="1"/>
-    <col min="14222" max="14222" width="8.7109375" style="2" customWidth="1"/>
-    <col min="14223" max="14223" width="10.28515625" style="2" customWidth="1"/>
+    <col min="14220" max="14220" width="5.88671875" style="2" customWidth="1"/>
+    <col min="14221" max="14221" width="31.44140625" style="2" customWidth="1"/>
+    <col min="14222" max="14222" width="8.6640625" style="2" customWidth="1"/>
+    <col min="14223" max="14223" width="10.33203125" style="2" customWidth="1"/>
     <col min="14224" max="14224" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="14225" max="14225" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14225" max="14225" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14226" max="14227" width="9" style="2"/>
-    <col min="14228" max="14228" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14228" max="14228" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14229" max="14229" width="9" style="2"/>
-    <col min="14230" max="14230" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14230" max="14230" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14231" max="14475" width="9" style="2"/>
-    <col min="14476" max="14476" width="5.85546875" style="2" customWidth="1"/>
-    <col min="14477" max="14477" width="31.42578125" style="2" customWidth="1"/>
-    <col min="14478" max="14478" width="8.7109375" style="2" customWidth="1"/>
-    <col min="14479" max="14479" width="10.28515625" style="2" customWidth="1"/>
+    <col min="14476" max="14476" width="5.88671875" style="2" customWidth="1"/>
+    <col min="14477" max="14477" width="31.44140625" style="2" customWidth="1"/>
+    <col min="14478" max="14478" width="8.6640625" style="2" customWidth="1"/>
+    <col min="14479" max="14479" width="10.33203125" style="2" customWidth="1"/>
     <col min="14480" max="14480" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="14481" max="14481" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14481" max="14481" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14482" max="14483" width="9" style="2"/>
-    <col min="14484" max="14484" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14484" max="14484" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14485" max="14485" width="9" style="2"/>
-    <col min="14486" max="14486" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14486" max="14486" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14487" max="14731" width="9" style="2"/>
-    <col min="14732" max="14732" width="5.85546875" style="2" customWidth="1"/>
-    <col min="14733" max="14733" width="31.42578125" style="2" customWidth="1"/>
-    <col min="14734" max="14734" width="8.7109375" style="2" customWidth="1"/>
-    <col min="14735" max="14735" width="10.28515625" style="2" customWidth="1"/>
+    <col min="14732" max="14732" width="5.88671875" style="2" customWidth="1"/>
+    <col min="14733" max="14733" width="31.44140625" style="2" customWidth="1"/>
+    <col min="14734" max="14734" width="8.6640625" style="2" customWidth="1"/>
+    <col min="14735" max="14735" width="10.33203125" style="2" customWidth="1"/>
     <col min="14736" max="14736" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="14737" max="14737" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14737" max="14737" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14738" max="14739" width="9" style="2"/>
-    <col min="14740" max="14740" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14740" max="14740" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14741" max="14741" width="9" style="2"/>
-    <col min="14742" max="14742" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14742" max="14742" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14743" max="14987" width="9" style="2"/>
-    <col min="14988" max="14988" width="5.85546875" style="2" customWidth="1"/>
-    <col min="14989" max="14989" width="31.42578125" style="2" customWidth="1"/>
-    <col min="14990" max="14990" width="8.7109375" style="2" customWidth="1"/>
-    <col min="14991" max="14991" width="10.28515625" style="2" customWidth="1"/>
+    <col min="14988" max="14988" width="5.88671875" style="2" customWidth="1"/>
+    <col min="14989" max="14989" width="31.44140625" style="2" customWidth="1"/>
+    <col min="14990" max="14990" width="8.6640625" style="2" customWidth="1"/>
+    <col min="14991" max="14991" width="10.33203125" style="2" customWidth="1"/>
     <col min="14992" max="14992" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="14993" max="14993" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14993" max="14993" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14994" max="14995" width="9" style="2"/>
-    <col min="14996" max="14996" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14996" max="14996" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14997" max="14997" width="9" style="2"/>
-    <col min="14998" max="14998" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14998" max="14998" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14999" max="15243" width="9" style="2"/>
-    <col min="15244" max="15244" width="5.85546875" style="2" customWidth="1"/>
-    <col min="15245" max="15245" width="31.42578125" style="2" customWidth="1"/>
-    <col min="15246" max="15246" width="8.7109375" style="2" customWidth="1"/>
-    <col min="15247" max="15247" width="10.28515625" style="2" customWidth="1"/>
+    <col min="15244" max="15244" width="5.88671875" style="2" customWidth="1"/>
+    <col min="15245" max="15245" width="31.44140625" style="2" customWidth="1"/>
+    <col min="15246" max="15246" width="8.6640625" style="2" customWidth="1"/>
+    <col min="15247" max="15247" width="10.33203125" style="2" customWidth="1"/>
     <col min="15248" max="15248" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="15249" max="15249" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15249" max="15249" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15250" max="15251" width="9" style="2"/>
-    <col min="15252" max="15252" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15252" max="15252" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15253" max="15253" width="9" style="2"/>
-    <col min="15254" max="15254" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15254" max="15254" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="15255" max="15499" width="9" style="2"/>
-    <col min="15500" max="15500" width="5.85546875" style="2" customWidth="1"/>
-    <col min="15501" max="15501" width="31.42578125" style="2" customWidth="1"/>
-    <col min="15502" max="15502" width="8.7109375" style="2" customWidth="1"/>
-    <col min="15503" max="15503" width="10.28515625" style="2" customWidth="1"/>
+    <col min="15500" max="15500" width="5.88671875" style="2" customWidth="1"/>
+    <col min="15501" max="15501" width="31.44140625" style="2" customWidth="1"/>
+    <col min="15502" max="15502" width="8.6640625" style="2" customWidth="1"/>
+    <col min="15503" max="15503" width="10.33203125" style="2" customWidth="1"/>
     <col min="15504" max="15504" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="15505" max="15505" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15505" max="15505" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15506" max="15507" width="9" style="2"/>
-    <col min="15508" max="15508" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15508" max="15508" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15509" max="15509" width="9" style="2"/>
-    <col min="15510" max="15510" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15510" max="15510" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="15511" max="15755" width="9" style="2"/>
-    <col min="15756" max="15756" width="5.85546875" style="2" customWidth="1"/>
-    <col min="15757" max="15757" width="31.42578125" style="2" customWidth="1"/>
-    <col min="15758" max="15758" width="8.7109375" style="2" customWidth="1"/>
-    <col min="15759" max="15759" width="10.28515625" style="2" customWidth="1"/>
+    <col min="15756" max="15756" width="5.88671875" style="2" customWidth="1"/>
+    <col min="15757" max="15757" width="31.44140625" style="2" customWidth="1"/>
+    <col min="15758" max="15758" width="8.6640625" style="2" customWidth="1"/>
+    <col min="15759" max="15759" width="10.33203125" style="2" customWidth="1"/>
     <col min="15760" max="15760" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="15761" max="15761" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15761" max="15761" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15762" max="15763" width="9" style="2"/>
-    <col min="15764" max="15764" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15764" max="15764" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15765" max="15765" width="9" style="2"/>
-    <col min="15766" max="15766" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15766" max="15766" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="15767" max="16011" width="9" style="2"/>
-    <col min="16012" max="16012" width="5.85546875" style="2" customWidth="1"/>
-    <col min="16013" max="16013" width="31.42578125" style="2" customWidth="1"/>
-    <col min="16014" max="16014" width="8.7109375" style="2" customWidth="1"/>
-    <col min="16015" max="16015" width="10.28515625" style="2" customWidth="1"/>
+    <col min="16012" max="16012" width="5.88671875" style="2" customWidth="1"/>
+    <col min="16013" max="16013" width="31.44140625" style="2" customWidth="1"/>
+    <col min="16014" max="16014" width="8.6640625" style="2" customWidth="1"/>
+    <col min="16015" max="16015" width="10.33203125" style="2" customWidth="1"/>
     <col min="16016" max="16016" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="16017" max="16017" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16017" max="16017" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="16018" max="16019" width="9" style="2"/>
-    <col min="16020" max="16020" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16020" max="16020" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="16021" max="16021" width="9" style="2"/>
-    <col min="16022" max="16022" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16022" max="16022" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="16023" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:9" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="9" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" s="14" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" spans="1:9" s="9" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:9" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="12">
         <v>200</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="13">
         <v>14000</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="13">
         <f t="shared" ref="F14" si="0">E14*D14</f>
         <v>2800000</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+    <row r="15" spans="1:9" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>3</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13">
         <v>200000</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20" t="s">
+    <row r="16" spans="1:9" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22">
+      <c r="C16" s="33"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16">
         <f>SUM(F14:F15)</f>
         <v>3000000</v>
       </c>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22">
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:9" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="23">
+        <v>0.08</v>
+      </c>
+      <c r="F17" s="16">
         <f>F16*8%</f>
         <v>240000</v>
       </c>
-      <c r="H17" s="24"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22">
+      <c r="H17" s="18"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16">
         <f>F16+F17</f>
         <v>3240000</v>
       </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="31" t="s">
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16">
+        <v>540000</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22">
-        <v>540000</v>
-      </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9" s="23" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22">
+      <c r="C20" s="27"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16">
         <f>F18-F19</f>
         <v>2700000</v>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="B22" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="I22" s="28"/>
-    </row>
-    <row r="23" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+    </row>
+    <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+    </row>
+    <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F28" s="28"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F28" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
+  <mergeCells count="16">
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="B19:C19"/>
@@ -1715,6 +1730,12 @@
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.5" bottom="0.75" header="0.05" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
